--- a/artfynd/A 20659-2024 artfynd.xlsx
+++ b/artfynd/A 20659-2024 artfynd.xlsx
@@ -1867,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117766511</v>
+        <v>117766509</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>78216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530730</v>
+        <v>530744</v>
       </c>
       <c r="R12" t="n">
-        <v>6911550</v>
+        <v>6911724</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117766509</v>
+        <v>117766511</v>
       </c>
       <c r="B13" t="n">
-        <v>78216</v>
+        <v>79561</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,21 +1994,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>530744</v>
+        <v>530730</v>
       </c>
       <c r="R13" t="n">
-        <v>6911724</v>
+        <v>6911550</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 20659-2024 artfynd.xlsx
+++ b/artfynd/A 20659-2024 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>117766509</v>
       </c>
       <c r="B12" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>117766511</v>
       </c>
       <c r="B13" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
